--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126829190</v>
       </c>
       <c r="B2" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126829103</v>
       </c>
       <c r="B3" t="n">
-        <v>75014</v>
+        <v>75073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126828821</v>
       </c>
       <c r="B5" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126828844</v>
       </c>
       <c r="B6" t="n">
-        <v>75014</v>
+        <v>75073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126828645</v>
       </c>
       <c r="B7" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126828747</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126829190</v>
       </c>
       <c r="B2" t="n">
-        <v>96562</v>
+        <v>96568</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126829103</v>
       </c>
       <c r="B3" t="n">
-        <v>75073</v>
+        <v>75076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126828821</v>
       </c>
       <c r="B5" t="n">
-        <v>96562</v>
+        <v>96568</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126828844</v>
       </c>
       <c r="B6" t="n">
-        <v>75073</v>
+        <v>75076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126828645</v>
       </c>
       <c r="B7" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126828747</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126829190</v>
       </c>
       <c r="B2" t="n">
-        <v>96568</v>
+        <v>96569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126828821</v>
       </c>
       <c r="B5" t="n">
-        <v>96568</v>
+        <v>96569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126828645</v>
       </c>
       <c r="B7" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126828747</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126829190</v>
       </c>
       <c r="B2" t="n">
-        <v>96569</v>
+        <v>96573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126829103</v>
       </c>
       <c r="B3" t="n">
-        <v>75076</v>
+        <v>75080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126828753</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126828821</v>
       </c>
       <c r="B5" t="n">
-        <v>96569</v>
+        <v>96573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126828844</v>
       </c>
       <c r="B6" t="n">
-        <v>75076</v>
+        <v>75080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126828645</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126828747</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>126828747</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126829190</v>
       </c>
       <c r="B2" t="n">
-        <v>96573</v>
+        <v>96562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126829103</v>
       </c>
       <c r="B3" t="n">
-        <v>75080</v>
+        <v>75073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126828753</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126828821</v>
       </c>
       <c r="B5" t="n">
-        <v>96573</v>
+        <v>96562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126828844</v>
       </c>
       <c r="B6" t="n">
-        <v>75080</v>
+        <v>75073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126828645</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126828747</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>98436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126829190</v>
       </c>
       <c r="B2" t="n">
-        <v>96562</v>
+        <v>96573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126829103</v>
       </c>
       <c r="B3" t="n">
-        <v>75073</v>
+        <v>75080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126828753</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126828821</v>
       </c>
       <c r="B5" t="n">
-        <v>96562</v>
+        <v>96573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126828844</v>
       </c>
       <c r="B6" t="n">
-        <v>75073</v>
+        <v>75080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>126828645</v>
       </c>
       <c r="B7" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>126828747</v>
       </c>
       <c r="B8" t="n">
-        <v>98436</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126829190</v>
+        <v>126828821</v>
       </c>
       <c r="B2" t="n">
-        <v>96573</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436373</v>
+        <v>436319</v>
       </c>
       <c r="R2" t="n">
-        <v>6760610</v>
+        <v>6760611</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126829103</v>
+        <v>126829190</v>
       </c>
       <c r="B3" t="n">
-        <v>75080</v>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436341</v>
+        <v>436373</v>
       </c>
       <c r="R3" t="n">
-        <v>6760608</v>
+        <v>6760610</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126828753</v>
+        <v>126828645</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,42 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Atugaturis, Atugaturis, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436329</v>
+        <v>436206</v>
       </c>
       <c r="R4" t="n">
-        <v>6760591</v>
+        <v>6760518</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126828821</v>
+        <v>126828844</v>
       </c>
       <c r="B5" t="n">
-        <v>96573</v>
+        <v>75428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436319</v>
+        <v>436318</v>
       </c>
       <c r="R5" t="n">
-        <v>6760611</v>
+        <v>6760589</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,14 +1103,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126828844</v>
+        <v>126829103</v>
       </c>
       <c r="B6" t="n">
-        <v>75080</v>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436318</v>
+        <v>436341</v>
       </c>
       <c r="R6" t="n">
-        <v>6760589</v>
+        <v>6760608</v>
       </c>
       <c r="S6" t="n">
         <v>9</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126828645</v>
+        <v>126828753</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,37 +1221,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Atugaturis, Atugaturis, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436206</v>
+        <v>436329</v>
       </c>
       <c r="R7" t="n">
-        <v>6760518</v>
+        <v>6760591</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,7 +1325,7 @@
         <v>126828747</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31539-2025 artfynd.xlsx
+++ b/artfynd/A 31539-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126829190</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126829103</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828753</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,8 +1475,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126828747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>